--- a/artfynd/A 41447-2024 artfynd.xlsx
+++ b/artfynd/A 41447-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487576</v>
+        <v>120487526</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440924</v>
+        <v>440561</v>
       </c>
       <c r="R2" t="n">
-        <v>6762515</v>
+        <v>6762628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487587</v>
+        <v>120487567</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440498</v>
+        <v>440437</v>
       </c>
       <c r="R3" t="n">
-        <v>6762553</v>
+        <v>6762574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487545</v>
+        <v>120487528</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,47 +900,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440451</v>
+        <v>440485</v>
       </c>
       <c r="R4" t="n">
-        <v>6762570</v>
+        <v>6762599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487531</v>
+        <v>120487557</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,34 +1006,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440460</v>
+        <v>440543</v>
       </c>
       <c r="R5" t="n">
-        <v>6762566</v>
+        <v>6762555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487599</v>
+        <v>120487584</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,47 +1113,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440668</v>
+        <v>440546</v>
       </c>
       <c r="R6" t="n">
-        <v>6762281</v>
+        <v>6762618</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487557</v>
+        <v>120487558</v>
       </c>
       <c r="B7" t="n">
-        <v>90864</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,31 +1219,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440543</v>
+        <v>440767</v>
       </c>
       <c r="R7" t="n">
-        <v>6762555</v>
+        <v>6762671</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487559</v>
+        <v>120487573</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>90594</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,21 +1330,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440510</v>
+        <v>440469</v>
       </c>
       <c r="R8" t="n">
-        <v>6762588</v>
+        <v>6762596</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487551</v>
+        <v>120487588</v>
       </c>
       <c r="B9" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,43 +1432,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440487</v>
+        <v>440541</v>
       </c>
       <c r="R9" t="n">
-        <v>6762567</v>
+        <v>6762542</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487581</v>
+        <v>120487531</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1543,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440773</v>
+        <v>440460</v>
       </c>
       <c r="R10" t="n">
-        <v>6762656</v>
+        <v>6762566</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487565</v>
+        <v>120487572</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>56524</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,47 +1632,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440511</v>
+        <v>440472</v>
       </c>
       <c r="R11" t="n">
-        <v>6762596</v>
+        <v>6762543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487550</v>
+        <v>120487547</v>
       </c>
       <c r="B12" t="n">
         <v>90864</v>
@@ -1789,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440488</v>
+        <v>440497</v>
       </c>
       <c r="R12" t="n">
-        <v>6762572</v>
+        <v>6762586</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487588</v>
+        <v>120487605</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,21 +1849,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440541</v>
+        <v>440554</v>
       </c>
       <c r="R13" t="n">
-        <v>6762542</v>
+        <v>6762397</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487543</v>
+        <v>120487578</v>
       </c>
       <c r="B14" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,47 +1947,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440483</v>
+        <v>440797</v>
       </c>
       <c r="R14" t="n">
-        <v>6762569</v>
+        <v>6762562</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487537</v>
+        <v>120487581</v>
       </c>
       <c r="B15" t="n">
-        <v>90600</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,21 +2053,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2104,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440446</v>
+        <v>440773</v>
       </c>
       <c r="R15" t="n">
-        <v>6762551</v>
+        <v>6762656</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487586</v>
+        <v>120487519</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2182,21 +2155,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2206,10 +2179,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440451</v>
+        <v>440543</v>
       </c>
       <c r="R16" t="n">
-        <v>6762538</v>
+        <v>6762378</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487589</v>
+        <v>120487556</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2284,34 +2257,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440562</v>
+        <v>440495</v>
       </c>
       <c r="R17" t="n">
-        <v>6762505</v>
+        <v>6762580</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487610</v>
+        <v>120487571</v>
       </c>
       <c r="B18" t="n">
-        <v>78187</v>
+        <v>78278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2386,21 +2368,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2410,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440703</v>
+        <v>440538</v>
       </c>
       <c r="R18" t="n">
-        <v>6762265</v>
+        <v>6762461</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487579</v>
+        <v>120487532</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2488,21 +2470,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2512,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440787</v>
+        <v>440434</v>
       </c>
       <c r="R19" t="n">
-        <v>6762574</v>
+        <v>6762573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487571</v>
+        <v>120487527</v>
       </c>
       <c r="B20" t="n">
-        <v>78278</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2590,21 +2572,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2614,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440538</v>
+        <v>440487</v>
       </c>
       <c r="R20" t="n">
-        <v>6762461</v>
+        <v>6762604</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487590</v>
+        <v>120487563</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2688,38 +2670,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440539</v>
+        <v>440538</v>
       </c>
       <c r="R21" t="n">
-        <v>6762467</v>
+        <v>6762562</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,10 +2769,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487554</v>
+        <v>120487544</v>
       </c>
       <c r="B22" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2790,25 +2781,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2827,10 +2818,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440451</v>
+        <v>440466</v>
       </c>
       <c r="R22" t="n">
-        <v>6762570</v>
+        <v>6762560</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2889,10 +2880,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120487546</v>
+        <v>120487585</v>
       </c>
       <c r="B23" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2901,47 +2892,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440451</v>
+        <v>440522</v>
       </c>
       <c r="R23" t="n">
-        <v>6762569</v>
+        <v>6762630</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3000,10 +2982,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120487573</v>
+        <v>120487599</v>
       </c>
       <c r="B24" t="n">
-        <v>90594</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3012,38 +2994,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440469</v>
+        <v>440668</v>
       </c>
       <c r="R24" t="n">
-        <v>6762596</v>
+        <v>6762281</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120487548</v>
+        <v>120487582</v>
       </c>
       <c r="B25" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3118,43 +3109,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440486</v>
+        <v>440609</v>
       </c>
       <c r="R25" t="n">
-        <v>6762603</v>
+        <v>6762652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3213,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120487572</v>
+        <v>120487606</v>
       </c>
       <c r="B26" t="n">
-        <v>56524</v>
+        <v>78187</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3253,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440472</v>
+        <v>440535</v>
       </c>
       <c r="R26" t="n">
-        <v>6762543</v>
+        <v>6762367</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3315,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120487607</v>
+        <v>120487555</v>
       </c>
       <c r="B27" t="n">
-        <v>78187</v>
+        <v>90864</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3331,34 +3313,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440557</v>
+        <v>440492</v>
       </c>
       <c r="R27" t="n">
-        <v>6762339</v>
+        <v>6762568</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,10 +3408,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120487604</v>
+        <v>120487576</v>
       </c>
       <c r="B28" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3433,21 +3424,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3457,10 +3448,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440546</v>
+        <v>440924</v>
       </c>
       <c r="R28" t="n">
-        <v>6762499</v>
+        <v>6762515</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3519,10 +3510,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120487558</v>
+        <v>120487609</v>
       </c>
       <c r="B29" t="n">
-        <v>91881</v>
+        <v>78187</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3535,43 +3526,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440767</v>
+        <v>440568</v>
       </c>
       <c r="R29" t="n">
-        <v>6762671</v>
+        <v>6762302</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3630,10 +3612,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120487568</v>
+        <v>120487530</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3642,47 +3624,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440543</v>
+        <v>440482</v>
       </c>
       <c r="R30" t="n">
-        <v>6762564</v>
+        <v>6762596</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3715,11 +3688,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,10 +3714,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120487547</v>
+        <v>120487565</v>
       </c>
       <c r="B31" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3758,35 +3726,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3795,10 +3763,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440497</v>
+        <v>440511</v>
       </c>
       <c r="R31" t="n">
-        <v>6762586</v>
+        <v>6762596</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3825,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120487569</v>
+        <v>120487539</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3869,35 +3837,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3906,10 +3870,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440493</v>
+        <v>440528</v>
       </c>
       <c r="R32" t="n">
-        <v>6762600</v>
+        <v>6762553</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3968,7 +3932,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120487578</v>
+        <v>120487590</v>
       </c>
       <c r="B33" t="n">
         <v>78542</v>
@@ -4008,10 +3972,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440797</v>
+        <v>440539</v>
       </c>
       <c r="R33" t="n">
-        <v>6762562</v>
+        <v>6762467</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4070,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120487609</v>
+        <v>120487570</v>
       </c>
       <c r="B34" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4082,38 +4046,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440568</v>
+        <v>440493</v>
       </c>
       <c r="R34" t="n">
-        <v>6762302</v>
+        <v>6762565</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4172,10 +4145,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120487549</v>
+        <v>120487569</v>
       </c>
       <c r="B35" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4184,35 +4157,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4221,10 +4194,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440478</v>
+        <v>440493</v>
       </c>
       <c r="R35" t="n">
-        <v>6762578</v>
+        <v>6762600</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120487544</v>
+        <v>120487603</v>
       </c>
       <c r="B36" t="n">
-        <v>91023</v>
+        <v>78187</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4295,47 +4268,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440466</v>
+        <v>440806</v>
       </c>
       <c r="R36" t="n">
-        <v>6762560</v>
+        <v>6762547</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4394,10 +4358,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120487527</v>
+        <v>120487607</v>
       </c>
       <c r="B37" t="n">
-        <v>90580</v>
+        <v>78187</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4410,21 +4374,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4434,10 +4398,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440487</v>
+        <v>440557</v>
       </c>
       <c r="R37" t="n">
-        <v>6762604</v>
+        <v>6762339</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4496,10 +4460,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120487533</v>
+        <v>120487549</v>
       </c>
       <c r="B38" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4512,34 +4476,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440545</v>
+        <v>440478</v>
       </c>
       <c r="R38" t="n">
-        <v>6762554</v>
+        <v>6762578</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4598,10 +4571,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120487563</v>
+        <v>120487543</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>91023</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4614,31 +4587,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4647,10 +4620,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440538</v>
+        <v>440483</v>
       </c>
       <c r="R39" t="n">
-        <v>6762562</v>
+        <v>6762569</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4709,10 +4682,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120487536</v>
+        <v>120487574</v>
       </c>
       <c r="B40" t="n">
-        <v>90600</v>
+        <v>90794</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4725,21 +4698,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5442</v>
+        <v>1101</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4749,10 +4722,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440753</v>
+        <v>440750</v>
       </c>
       <c r="R40" t="n">
-        <v>6762641</v>
+        <v>6762682</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4793,6 +4766,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4811,10 +4785,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120487556</v>
+        <v>120487583</v>
       </c>
       <c r="B41" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4827,43 +4801,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440495</v>
+        <v>440558</v>
       </c>
       <c r="R41" t="n">
-        <v>6762580</v>
+        <v>6762625</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4922,10 +4887,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120487528</v>
+        <v>120487589</v>
       </c>
       <c r="B42" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4938,21 +4903,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4962,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440485</v>
+        <v>440562</v>
       </c>
       <c r="R42" t="n">
-        <v>6762599</v>
+        <v>6762505</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5024,10 +4989,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120487530</v>
+        <v>120487604</v>
       </c>
       <c r="B43" t="n">
-        <v>90580</v>
+        <v>78187</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5040,21 +5005,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5064,10 +5029,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440482</v>
+        <v>440546</v>
       </c>
       <c r="R43" t="n">
-        <v>6762596</v>
+        <v>6762499</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5126,10 +5091,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120487606</v>
+        <v>120487552</v>
       </c>
       <c r="B44" t="n">
-        <v>78187</v>
+        <v>90864</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5142,34 +5107,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440535</v>
+        <v>440453</v>
       </c>
       <c r="R44" t="n">
-        <v>6762367</v>
+        <v>6762573</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5228,10 +5202,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120487552</v>
+        <v>120487568</v>
       </c>
       <c r="B45" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5240,35 +5214,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5277,10 +5251,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440453</v>
+        <v>440543</v>
       </c>
       <c r="R45" t="n">
-        <v>6762573</v>
+        <v>6762564</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5313,6 +5287,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5339,10 +5318,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120487539</v>
+        <v>120487559</v>
       </c>
       <c r="B46" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5355,39 +5334,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440528</v>
+        <v>440510</v>
       </c>
       <c r="R46" t="n">
-        <v>6762553</v>
+        <v>6762588</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5446,10 +5420,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120487603</v>
+        <v>120487553</v>
       </c>
       <c r="B47" t="n">
-        <v>78187</v>
+        <v>90864</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5462,34 +5436,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440806</v>
+        <v>440453</v>
       </c>
       <c r="R47" t="n">
-        <v>6762547</v>
+        <v>6762571</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5548,10 +5531,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120487519</v>
+        <v>120487542</v>
       </c>
       <c r="B48" t="n">
-        <v>79160</v>
+        <v>91023</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5560,38 +5543,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440543</v>
+        <v>440487</v>
       </c>
       <c r="R48" t="n">
-        <v>6762378</v>
+        <v>6762566</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5650,10 +5642,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120487583</v>
+        <v>120487554</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5666,34 +5658,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440558</v>
+        <v>440451</v>
       </c>
       <c r="R49" t="n">
-        <v>6762625</v>
+        <v>6762570</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5752,10 +5753,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120487532</v>
+        <v>120487546</v>
       </c>
       <c r="B50" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5764,38 +5765,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440434</v>
+        <v>440451</v>
       </c>
       <c r="R50" t="n">
-        <v>6762573</v>
+        <v>6762569</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5854,7 +5864,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120487555</v>
+        <v>120487551</v>
       </c>
       <c r="B51" t="n">
         <v>90864</v>
@@ -5903,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440492</v>
+        <v>440487</v>
       </c>
       <c r="R51" t="n">
-        <v>6762568</v>
+        <v>6762567</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5965,7 +5975,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120487584</v>
+        <v>120487579</v>
       </c>
       <c r="B52" t="n">
         <v>78542</v>
@@ -6005,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440546</v>
+        <v>440787</v>
       </c>
       <c r="R52" t="n">
-        <v>6762618</v>
+        <v>6762574</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6067,10 +6077,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120487570</v>
+        <v>120487577</v>
       </c>
       <c r="B53" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6079,47 +6089,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440493</v>
+        <v>440831</v>
       </c>
       <c r="R53" t="n">
-        <v>6762565</v>
+        <v>6762542</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6178,10 +6179,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120487526</v>
+        <v>120487545</v>
       </c>
       <c r="B54" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6190,38 +6191,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440561</v>
+        <v>440451</v>
       </c>
       <c r="R54" t="n">
-        <v>6762628</v>
+        <v>6762570</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6280,10 +6290,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120487567</v>
+        <v>120487586</v>
       </c>
       <c r="B55" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6292,47 +6302,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440437</v>
+        <v>440451</v>
       </c>
       <c r="R55" t="n">
-        <v>6762574</v>
+        <v>6762538</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6391,10 +6392,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120487520</v>
+        <v>120487587</v>
       </c>
       <c r="B56" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6407,21 +6408,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6431,10 +6432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440548</v>
+        <v>440498</v>
       </c>
       <c r="R56" t="n">
-        <v>6762339</v>
+        <v>6762553</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6493,10 +6494,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120487542</v>
+        <v>120487537</v>
       </c>
       <c r="B57" t="n">
-        <v>91023</v>
+        <v>90600</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6505,47 +6506,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440487</v>
+        <v>440446</v>
       </c>
       <c r="R57" t="n">
-        <v>6762566</v>
+        <v>6762551</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6604,10 +6596,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120487574</v>
+        <v>120487550</v>
       </c>
       <c r="B58" t="n">
-        <v>90794</v>
+        <v>90864</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6620,34 +6612,43 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1101</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440750</v>
+        <v>440488</v>
       </c>
       <c r="R58" t="n">
-        <v>6762682</v>
+        <v>6762572</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6688,7 +6689,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6707,10 +6707,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120487585</v>
+        <v>120487548</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6723,34 +6723,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440522</v>
+        <v>440486</v>
       </c>
       <c r="R59" t="n">
-        <v>6762630</v>
+        <v>6762603</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6809,7 +6818,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120487605</v>
+        <v>120487610</v>
       </c>
       <c r="B60" t="n">
         <v>78187</v>
@@ -6849,10 +6858,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440554</v>
+        <v>440703</v>
       </c>
       <c r="R60" t="n">
-        <v>6762397</v>
+        <v>6762265</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6911,10 +6920,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120487577</v>
+        <v>120487536</v>
       </c>
       <c r="B61" t="n">
-        <v>78542</v>
+        <v>90600</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6927,21 +6936,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6951,10 +6960,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440831</v>
+        <v>440753</v>
       </c>
       <c r="R61" t="n">
-        <v>6762542</v>
+        <v>6762641</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7013,7 +7022,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120487582</v>
+        <v>120487580</v>
       </c>
       <c r="B62" t="n">
         <v>78542</v>
@@ -7053,10 +7062,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440609</v>
+        <v>440773</v>
       </c>
       <c r="R62" t="n">
-        <v>6762652</v>
+        <v>6762583</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7115,10 +7124,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120487580</v>
+        <v>120487533</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7131,21 +7140,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7155,10 +7164,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440773</v>
+        <v>440545</v>
       </c>
       <c r="R63" t="n">
-        <v>6762583</v>
+        <v>6762554</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7217,10 +7226,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120487553</v>
+        <v>120487520</v>
       </c>
       <c r="B64" t="n">
-        <v>90864</v>
+        <v>79160</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7233,43 +7242,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440453</v>
+        <v>440548</v>
       </c>
       <c r="R64" t="n">
-        <v>6762571</v>
+        <v>6762339</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 41447-2024 artfynd.xlsx
+++ b/artfynd/A 41447-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487526</v>
+        <v>120487580</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440561</v>
+        <v>440773</v>
       </c>
       <c r="R2" t="n">
-        <v>6762628</v>
+        <v>6762583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487567</v>
+        <v>120487569</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440437</v>
+        <v>440493</v>
       </c>
       <c r="R3" t="n">
-        <v>6762574</v>
+        <v>6762600</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487528</v>
+        <v>120487543</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +900,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440485</v>
+        <v>440483</v>
       </c>
       <c r="R4" t="n">
-        <v>6762599</v>
+        <v>6762569</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487557</v>
+        <v>120487537</v>
       </c>
       <c r="B5" t="n">
-        <v>90864</v>
+        <v>90600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,43 +1015,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440543</v>
+        <v>440446</v>
       </c>
       <c r="R5" t="n">
-        <v>6762555</v>
+        <v>6762551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487584</v>
+        <v>120487573</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440546</v>
+        <v>440469</v>
       </c>
       <c r="R6" t="n">
-        <v>6762618</v>
+        <v>6762596</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487558</v>
+        <v>120487606</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>78187</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,43 +1219,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440767</v>
+        <v>440535</v>
       </c>
       <c r="R7" t="n">
-        <v>6762671</v>
+        <v>6762367</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487573</v>
+        <v>120487584</v>
       </c>
       <c r="B8" t="n">
-        <v>90594</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1330,21 +1321,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440469</v>
+        <v>440546</v>
       </c>
       <c r="R8" t="n">
-        <v>6762596</v>
+        <v>6762618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487588</v>
+        <v>120487539</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,34 +1423,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440541</v>
+        <v>440528</v>
       </c>
       <c r="R9" t="n">
-        <v>6762542</v>
+        <v>6762553</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487531</v>
+        <v>120487604</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>78187</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,21 +1530,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440460</v>
+        <v>440546</v>
       </c>
       <c r="R10" t="n">
-        <v>6762566</v>
+        <v>6762499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487572</v>
+        <v>120487558</v>
       </c>
       <c r="B11" t="n">
-        <v>56524</v>
+        <v>91881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,34 +1632,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440472</v>
+        <v>440767</v>
       </c>
       <c r="R11" t="n">
-        <v>6762543</v>
+        <v>6762671</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487547</v>
+        <v>120487576</v>
       </c>
       <c r="B12" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1738,43 +1743,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440497</v>
+        <v>440924</v>
       </c>
       <c r="R12" t="n">
-        <v>6762586</v>
+        <v>6762515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487605</v>
+        <v>120487588</v>
       </c>
       <c r="B13" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1849,21 +1845,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1873,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440554</v>
+        <v>440541</v>
       </c>
       <c r="R13" t="n">
-        <v>6762397</v>
+        <v>6762542</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,10 +1931,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487578</v>
+        <v>120487605</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,21 +1947,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1975,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440797</v>
+        <v>440554</v>
       </c>
       <c r="R14" t="n">
-        <v>6762562</v>
+        <v>6762397</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487581</v>
+        <v>120487530</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,21 +2049,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440773</v>
+        <v>440482</v>
       </c>
       <c r="R15" t="n">
-        <v>6762656</v>
+        <v>6762596</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487519</v>
+        <v>120487542</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>91023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,38 +2147,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440543</v>
+        <v>440487</v>
       </c>
       <c r="R16" t="n">
-        <v>6762378</v>
+        <v>6762566</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,7 +2246,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487556</v>
+        <v>120487548</v>
       </c>
       <c r="B17" t="n">
         <v>90864</v>
@@ -2290,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440495</v>
+        <v>440486</v>
       </c>
       <c r="R17" t="n">
-        <v>6762580</v>
+        <v>6762603</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487571</v>
+        <v>120487557</v>
       </c>
       <c r="B18" t="n">
-        <v>78278</v>
+        <v>90864</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,34 +2373,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440538</v>
+        <v>440543</v>
       </c>
       <c r="R18" t="n">
-        <v>6762461</v>
+        <v>6762555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,10 +2468,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487532</v>
+        <v>120487549</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2470,34 +2484,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440434</v>
+        <v>440478</v>
       </c>
       <c r="R19" t="n">
-        <v>6762573</v>
+        <v>6762578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,10 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487527</v>
+        <v>120487536</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>90600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2572,21 +2595,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440487</v>
+        <v>440753</v>
       </c>
       <c r="R20" t="n">
-        <v>6762604</v>
+        <v>6762641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2658,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487563</v>
+        <v>120487533</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2670,47 +2693,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440538</v>
+        <v>440545</v>
       </c>
       <c r="R21" t="n">
-        <v>6762562</v>
+        <v>6762554</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,10 +2783,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487544</v>
+        <v>120487550</v>
       </c>
       <c r="B22" t="n">
-        <v>91023</v>
+        <v>90864</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2781,25 +2795,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2818,10 +2832,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440466</v>
+        <v>440488</v>
       </c>
       <c r="R22" t="n">
-        <v>6762560</v>
+        <v>6762572</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,10 +2894,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120487585</v>
+        <v>120487544</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2892,38 +2906,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440522</v>
+        <v>440466</v>
       </c>
       <c r="R23" t="n">
-        <v>6762630</v>
+        <v>6762560</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,10 +3005,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120487599</v>
+        <v>120487545</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>91023</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2994,25 +3017,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3031,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440668</v>
+        <v>440451</v>
       </c>
       <c r="R24" t="n">
-        <v>6762281</v>
+        <v>6762570</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120487582</v>
+        <v>120487528</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3109,21 +3132,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3133,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440609</v>
+        <v>440485</v>
       </c>
       <c r="R25" t="n">
-        <v>6762652</v>
+        <v>6762599</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120487606</v>
+        <v>120487520</v>
       </c>
       <c r="B26" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3211,21 +3234,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440535</v>
+        <v>440548</v>
       </c>
       <c r="R26" t="n">
-        <v>6762367</v>
+        <v>6762339</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3297,10 +3320,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120487555</v>
+        <v>120487585</v>
       </c>
       <c r="B27" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3313,43 +3336,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440492</v>
+        <v>440522</v>
       </c>
       <c r="R27" t="n">
-        <v>6762568</v>
+        <v>6762630</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,10 +3422,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120487576</v>
+        <v>120487519</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3424,21 +3438,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3448,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440924</v>
+        <v>440543</v>
       </c>
       <c r="R28" t="n">
-        <v>6762515</v>
+        <v>6762378</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3510,10 +3524,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120487609</v>
+        <v>120487556</v>
       </c>
       <c r="B29" t="n">
-        <v>78187</v>
+        <v>90864</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3526,34 +3540,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440568</v>
+        <v>440495</v>
       </c>
       <c r="R29" t="n">
-        <v>6762302</v>
+        <v>6762580</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3612,10 +3635,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120487530</v>
+        <v>120487610</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>78187</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3628,21 +3651,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3652,10 +3675,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440482</v>
+        <v>440703</v>
       </c>
       <c r="R30" t="n">
-        <v>6762596</v>
+        <v>6762265</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3714,10 +3737,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120487565</v>
+        <v>120487559</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3726,47 +3749,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440511</v>
+        <v>440510</v>
       </c>
       <c r="R31" t="n">
-        <v>6762596</v>
+        <v>6762588</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,10 +3839,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120487539</v>
+        <v>120487582</v>
       </c>
       <c r="B32" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3841,39 +3855,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440528</v>
+        <v>440609</v>
       </c>
       <c r="R32" t="n">
-        <v>6762553</v>
+        <v>6762652</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,10 +3941,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120487590</v>
+        <v>120487568</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3944,38 +3953,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440539</v>
+        <v>440543</v>
       </c>
       <c r="R33" t="n">
-        <v>6762467</v>
+        <v>6762564</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,6 +4026,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4034,10 +4057,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120487570</v>
+        <v>120487531</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4046,47 +4069,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440493</v>
+        <v>440460</v>
       </c>
       <c r="R34" t="n">
-        <v>6762565</v>
+        <v>6762566</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4145,10 +4159,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120487569</v>
+        <v>120487607</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4157,47 +4171,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440493</v>
+        <v>440557</v>
       </c>
       <c r="R35" t="n">
-        <v>6762600</v>
+        <v>6762339</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4256,10 +4261,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120487603</v>
+        <v>120487527</v>
       </c>
       <c r="B36" t="n">
-        <v>78187</v>
+        <v>90580</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4272,21 +4277,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4296,10 +4301,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440806</v>
+        <v>440487</v>
       </c>
       <c r="R36" t="n">
-        <v>6762547</v>
+        <v>6762604</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,10 +4363,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120487607</v>
+        <v>120487552</v>
       </c>
       <c r="B37" t="n">
-        <v>78187</v>
+        <v>90864</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4374,34 +4379,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440557</v>
+        <v>440453</v>
       </c>
       <c r="R37" t="n">
-        <v>6762339</v>
+        <v>6762573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4460,10 +4474,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120487549</v>
+        <v>120487583</v>
       </c>
       <c r="B38" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4476,43 +4490,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440478</v>
+        <v>440558</v>
       </c>
       <c r="R38" t="n">
-        <v>6762578</v>
+        <v>6762625</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4571,10 +4576,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120487543</v>
+        <v>120487590</v>
       </c>
       <c r="B39" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4583,47 +4588,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440483</v>
+        <v>440539</v>
       </c>
       <c r="R39" t="n">
-        <v>6762569</v>
+        <v>6762467</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4682,10 +4678,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120487574</v>
+        <v>120487586</v>
       </c>
       <c r="B40" t="n">
-        <v>90794</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4698,21 +4694,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1101</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4722,10 +4718,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440750</v>
+        <v>440451</v>
       </c>
       <c r="R40" t="n">
-        <v>6762682</v>
+        <v>6762538</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4766,7 +4762,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4785,10 +4780,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120487583</v>
+        <v>120487532</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4801,21 +4796,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4825,10 +4820,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440558</v>
+        <v>440434</v>
       </c>
       <c r="R41" t="n">
-        <v>6762625</v>
+        <v>6762573</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4887,10 +4882,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120487589</v>
+        <v>120487553</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4903,34 +4898,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440562</v>
+        <v>440453</v>
       </c>
       <c r="R42" t="n">
-        <v>6762505</v>
+        <v>6762571</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,7 +4993,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120487604</v>
+        <v>120487609</v>
       </c>
       <c r="B43" t="n">
         <v>78187</v>
@@ -5029,10 +5033,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440546</v>
+        <v>440568</v>
       </c>
       <c r="R43" t="n">
-        <v>6762499</v>
+        <v>6762302</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,10 +5095,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120487552</v>
+        <v>120487579</v>
       </c>
       <c r="B44" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5107,43 +5111,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440453</v>
+        <v>440787</v>
       </c>
       <c r="R44" t="n">
-        <v>6762573</v>
+        <v>6762574</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5202,10 +5197,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120487568</v>
+        <v>120487571</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5214,47 +5209,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440543</v>
+        <v>440538</v>
       </c>
       <c r="R45" t="n">
-        <v>6762564</v>
+        <v>6762461</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5287,11 +5273,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5318,10 +5299,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120487559</v>
+        <v>120487572</v>
       </c>
       <c r="B46" t="n">
-        <v>79623</v>
+        <v>56524</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5334,21 +5315,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5358,10 +5339,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440510</v>
+        <v>440472</v>
       </c>
       <c r="R46" t="n">
-        <v>6762588</v>
+        <v>6762543</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5420,10 +5401,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120487553</v>
+        <v>120487563</v>
       </c>
       <c r="B47" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5432,35 +5413,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5469,10 +5450,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440453</v>
+        <v>440538</v>
       </c>
       <c r="R47" t="n">
-        <v>6762571</v>
+        <v>6762562</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5531,10 +5512,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120487542</v>
+        <v>120487603</v>
       </c>
       <c r="B48" t="n">
-        <v>91023</v>
+        <v>78187</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5543,47 +5524,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440487</v>
+        <v>440806</v>
       </c>
       <c r="R48" t="n">
-        <v>6762566</v>
+        <v>6762547</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5642,7 +5614,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120487554</v>
+        <v>120487547</v>
       </c>
       <c r="B49" t="n">
         <v>90864</v>
@@ -5691,10 +5663,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440451</v>
+        <v>440497</v>
       </c>
       <c r="R49" t="n">
-        <v>6762570</v>
+        <v>6762586</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5753,10 +5725,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120487546</v>
+        <v>120487555</v>
       </c>
       <c r="B50" t="n">
-        <v>91023</v>
+        <v>90864</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5765,25 +5737,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5802,10 +5774,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440451</v>
+        <v>440492</v>
       </c>
       <c r="R50" t="n">
-        <v>6762569</v>
+        <v>6762568</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5864,10 +5836,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120487551</v>
+        <v>120487589</v>
       </c>
       <c r="B51" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5880,43 +5852,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440487</v>
+        <v>440562</v>
       </c>
       <c r="R51" t="n">
-        <v>6762567</v>
+        <v>6762505</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5975,7 +5938,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120487579</v>
+        <v>120487587</v>
       </c>
       <c r="B52" t="n">
         <v>78542</v>
@@ -6015,10 +5978,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440787</v>
+        <v>440498</v>
       </c>
       <c r="R52" t="n">
-        <v>6762574</v>
+        <v>6762553</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6077,10 +6040,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120487577</v>
+        <v>120487546</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6089,38 +6052,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440831</v>
+        <v>440451</v>
       </c>
       <c r="R53" t="n">
-        <v>6762542</v>
+        <v>6762569</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6179,10 +6151,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120487545</v>
+        <v>120487565</v>
       </c>
       <c r="B54" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6195,31 +6167,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6228,10 +6200,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440451</v>
+        <v>440511</v>
       </c>
       <c r="R54" t="n">
-        <v>6762570</v>
+        <v>6762596</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6290,10 +6262,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120487586</v>
+        <v>120487567</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6302,38 +6274,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440451</v>
+        <v>440437</v>
       </c>
       <c r="R55" t="n">
-        <v>6762538</v>
+        <v>6762574</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6392,7 +6373,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120487587</v>
+        <v>120487578</v>
       </c>
       <c r="B56" t="n">
         <v>78542</v>
@@ -6432,10 +6413,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440498</v>
+        <v>440797</v>
       </c>
       <c r="R56" t="n">
-        <v>6762553</v>
+        <v>6762562</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6494,10 +6475,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120487537</v>
+        <v>120487551</v>
       </c>
       <c r="B57" t="n">
-        <v>90600</v>
+        <v>90864</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6510,34 +6491,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440446</v>
+        <v>440487</v>
       </c>
       <c r="R57" t="n">
-        <v>6762551</v>
+        <v>6762567</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6596,10 +6586,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120487550</v>
+        <v>120487526</v>
       </c>
       <c r="B58" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6612,43 +6602,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440488</v>
+        <v>440561</v>
       </c>
       <c r="R58" t="n">
-        <v>6762572</v>
+        <v>6762628</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6707,7 +6688,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120487548</v>
+        <v>120487554</v>
       </c>
       <c r="B59" t="n">
         <v>90864</v>
@@ -6756,10 +6737,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440486</v>
+        <v>440451</v>
       </c>
       <c r="R59" t="n">
-        <v>6762603</v>
+        <v>6762570</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6818,10 +6799,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120487610</v>
+        <v>120487574</v>
       </c>
       <c r="B60" t="n">
-        <v>78187</v>
+        <v>90794</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6834,21 +6815,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>1101</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6858,10 +6839,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440703</v>
+        <v>440750</v>
       </c>
       <c r="R60" t="n">
-        <v>6762265</v>
+        <v>6762682</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6902,6 +6883,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6920,10 +6902,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120487536</v>
+        <v>120487570</v>
       </c>
       <c r="B61" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6932,38 +6914,47 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440753</v>
+        <v>440493</v>
       </c>
       <c r="R61" t="n">
-        <v>6762641</v>
+        <v>6762565</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7022,7 +7013,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120487580</v>
+        <v>120487581</v>
       </c>
       <c r="B62" t="n">
         <v>78542</v>
@@ -7065,7 +7056,7 @@
         <v>440773</v>
       </c>
       <c r="R62" t="n">
-        <v>6762583</v>
+        <v>6762656</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7124,10 +7115,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120487533</v>
+        <v>120487577</v>
       </c>
       <c r="B63" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7140,21 +7131,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7164,10 +7155,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440545</v>
+        <v>440831</v>
       </c>
       <c r="R63" t="n">
-        <v>6762554</v>
+        <v>6762542</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7226,10 +7217,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120487520</v>
+        <v>120487599</v>
       </c>
       <c r="B64" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7238,38 +7229,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440548</v>
+        <v>440668</v>
       </c>
       <c r="R64" t="n">
-        <v>6762339</v>
+        <v>6762281</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 41447-2024 artfynd.xlsx
+++ b/artfynd/A 41447-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487580</v>
+        <v>120487586</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440773</v>
+        <v>440451</v>
       </c>
       <c r="R2" t="n">
-        <v>6762583</v>
+        <v>6762538</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487569</v>
+        <v>120487603</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440493</v>
+        <v>440806</v>
       </c>
       <c r="R3" t="n">
-        <v>6762600</v>
+        <v>6762547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487543</v>
+        <v>120487605</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
+        <v>78187</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,47 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440483</v>
+        <v>440554</v>
       </c>
       <c r="R4" t="n">
-        <v>6762569</v>
+        <v>6762397</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487537</v>
+        <v>120487536</v>
       </c>
       <c r="B5" t="n">
         <v>90600</v>
@@ -1039,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440446</v>
+        <v>440753</v>
       </c>
       <c r="R5" t="n">
-        <v>6762551</v>
+        <v>6762641</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487573</v>
+        <v>120487551</v>
       </c>
       <c r="B6" t="n">
-        <v>90594</v>
+        <v>90864</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,34 +1099,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440469</v>
+        <v>440487</v>
       </c>
       <c r="R6" t="n">
-        <v>6762596</v>
+        <v>6762567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487606</v>
+        <v>120487580</v>
       </c>
       <c r="B7" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440535</v>
+        <v>440773</v>
       </c>
       <c r="R7" t="n">
-        <v>6762367</v>
+        <v>6762583</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487584</v>
+        <v>120487607</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440546</v>
+        <v>440557</v>
       </c>
       <c r="R8" t="n">
-        <v>6762618</v>
+        <v>6762339</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487539</v>
+        <v>120487550</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,27 +1414,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1452,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440528</v>
+        <v>440488</v>
       </c>
       <c r="R9" t="n">
-        <v>6762553</v>
+        <v>6762572</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487604</v>
+        <v>120487555</v>
       </c>
       <c r="B10" t="n">
-        <v>78187</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1530,34 +1525,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440546</v>
+        <v>440492</v>
       </c>
       <c r="R10" t="n">
-        <v>6762499</v>
+        <v>6762568</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487558</v>
+        <v>120487557</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>90864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1632,31 +1636,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1665,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440767</v>
+        <v>440543</v>
       </c>
       <c r="R11" t="n">
-        <v>6762671</v>
+        <v>6762555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487576</v>
+        <v>120487571</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1767,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440924</v>
+        <v>440538</v>
       </c>
       <c r="R12" t="n">
-        <v>6762515</v>
+        <v>6762461</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487588</v>
+        <v>120487554</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,34 +1849,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440541</v>
+        <v>440451</v>
       </c>
       <c r="R13" t="n">
-        <v>6762542</v>
+        <v>6762570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487605</v>
+        <v>120487520</v>
       </c>
       <c r="B14" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1947,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1971,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440554</v>
+        <v>440548</v>
       </c>
       <c r="R14" t="n">
-        <v>6762397</v>
+        <v>6762339</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487530</v>
+        <v>120487587</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2049,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2073,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440482</v>
+        <v>440498</v>
       </c>
       <c r="R15" t="n">
-        <v>6762596</v>
+        <v>6762553</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487542</v>
+        <v>120487590</v>
       </c>
       <c r="B16" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,47 +2160,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440487</v>
+        <v>440539</v>
       </c>
       <c r="R16" t="n">
-        <v>6762566</v>
+        <v>6762467</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487548</v>
+        <v>120487567</v>
       </c>
       <c r="B17" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2258,35 +2262,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2295,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440486</v>
+        <v>440437</v>
       </c>
       <c r="R17" t="n">
-        <v>6762603</v>
+        <v>6762574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,10 +2361,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487557</v>
+        <v>120487584</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,43 +2377,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440543</v>
+        <v>440546</v>
       </c>
       <c r="R18" t="n">
-        <v>6762555</v>
+        <v>6762618</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2468,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487549</v>
+        <v>120487565</v>
       </c>
       <c r="B19" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,35 +2475,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2517,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440478</v>
+        <v>440511</v>
       </c>
       <c r="R19" t="n">
-        <v>6762578</v>
+        <v>6762596</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,10 +2574,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487536</v>
+        <v>120487606</v>
       </c>
       <c r="B20" t="n">
-        <v>90600</v>
+        <v>78187</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,21 +2590,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2619,10 +2614,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440753</v>
+        <v>440535</v>
       </c>
       <c r="R20" t="n">
-        <v>6762641</v>
+        <v>6762367</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,10 +2676,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487533</v>
+        <v>120487572</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>56524</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,21 +2692,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2721,10 +2716,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440545</v>
+        <v>440472</v>
       </c>
       <c r="R21" t="n">
-        <v>6762554</v>
+        <v>6762543</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,10 +2778,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487550</v>
+        <v>120487581</v>
       </c>
       <c r="B22" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,43 +2794,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440488</v>
+        <v>440773</v>
       </c>
       <c r="R22" t="n">
-        <v>6762572</v>
+        <v>6762656</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,10 +2880,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120487544</v>
+        <v>120487563</v>
       </c>
       <c r="B23" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,31 +2896,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2943,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>440466</v>
+        <v>440538</v>
       </c>
       <c r="R23" t="n">
-        <v>6762560</v>
+        <v>6762562</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,10 +2991,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120487545</v>
+        <v>120487549</v>
       </c>
       <c r="B24" t="n">
-        <v>91023</v>
+        <v>90864</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,25 +3003,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3054,10 +3040,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>440451</v>
+        <v>440478</v>
       </c>
       <c r="R24" t="n">
-        <v>6762570</v>
+        <v>6762578</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3116,10 +3102,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120487528</v>
+        <v>120487548</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,34 +3118,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>440485</v>
+        <v>440486</v>
       </c>
       <c r="R25" t="n">
-        <v>6762599</v>
+        <v>6762603</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3218,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120487520</v>
+        <v>120487544</v>
       </c>
       <c r="B26" t="n">
-        <v>79160</v>
+        <v>91023</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3230,38 +3225,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>440548</v>
+        <v>440466</v>
       </c>
       <c r="R26" t="n">
-        <v>6762339</v>
+        <v>6762560</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,10 +3324,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120487585</v>
+        <v>120487599</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3332,38 +3336,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>440522</v>
+        <v>440668</v>
       </c>
       <c r="R27" t="n">
-        <v>6762630</v>
+        <v>6762281</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120487519</v>
+        <v>120487558</v>
       </c>
       <c r="B28" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3438,34 +3451,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>440543</v>
+        <v>440767</v>
       </c>
       <c r="R28" t="n">
-        <v>6762378</v>
+        <v>6762671</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120487556</v>
+        <v>120487539</v>
       </c>
       <c r="B29" t="n">
-        <v>90864</v>
+        <v>57336</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,31 +3562,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3573,10 +3591,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>440495</v>
+        <v>440528</v>
       </c>
       <c r="R29" t="n">
-        <v>6762580</v>
+        <v>6762553</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120487610</v>
+        <v>120487573</v>
       </c>
       <c r="B30" t="n">
-        <v>78187</v>
+        <v>90594</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,21 +3669,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3675,10 +3693,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>440703</v>
+        <v>440469</v>
       </c>
       <c r="R30" t="n">
-        <v>6762265</v>
+        <v>6762596</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3737,10 +3755,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120487559</v>
+        <v>120487545</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>91023</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3749,38 +3767,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>440510</v>
+        <v>440451</v>
       </c>
       <c r="R31" t="n">
-        <v>6762588</v>
+        <v>6762570</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3839,10 +3866,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120487582</v>
+        <v>120487530</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3855,21 +3882,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3879,10 +3906,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>440609</v>
+        <v>440482</v>
       </c>
       <c r="R32" t="n">
-        <v>6762652</v>
+        <v>6762596</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,10 +3968,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120487568</v>
+        <v>120487527</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3953,47 +3980,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>440543</v>
+        <v>440487</v>
       </c>
       <c r="R33" t="n">
-        <v>6762564</v>
+        <v>6762604</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4026,11 +4044,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4057,10 +4070,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120487531</v>
+        <v>120487543</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,38 +4082,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440460</v>
+        <v>440483</v>
       </c>
       <c r="R34" t="n">
-        <v>6762566</v>
+        <v>6762569</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4159,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120487607</v>
+        <v>120487528</v>
       </c>
       <c r="B35" t="n">
-        <v>78187</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,21 +4197,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4199,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440557</v>
+        <v>440485</v>
       </c>
       <c r="R35" t="n">
-        <v>6762339</v>
+        <v>6762599</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4261,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120487527</v>
+        <v>120487547</v>
       </c>
       <c r="B36" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4277,34 +4299,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>440487</v>
+        <v>440497</v>
       </c>
       <c r="R36" t="n">
-        <v>6762604</v>
+        <v>6762586</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4363,10 +4394,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120487552</v>
+        <v>120487585</v>
       </c>
       <c r="B37" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4379,43 +4410,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>440453</v>
+        <v>440522</v>
       </c>
       <c r="R37" t="n">
-        <v>6762573</v>
+        <v>6762630</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,10 +4598,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120487590</v>
+        <v>120487559</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4592,21 +4614,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4616,10 +4638,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>440539</v>
+        <v>440510</v>
       </c>
       <c r="R39" t="n">
-        <v>6762467</v>
+        <v>6762588</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,10 +4700,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120487586</v>
+        <v>120487609</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4694,21 +4716,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4718,10 +4740,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440451</v>
+        <v>440568</v>
       </c>
       <c r="R40" t="n">
-        <v>6762538</v>
+        <v>6762302</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4780,7 +4802,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120487532</v>
+        <v>120487533</v>
       </c>
       <c r="B41" t="n">
         <v>90580</v>
@@ -4820,10 +4842,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440434</v>
+        <v>440545</v>
       </c>
       <c r="R41" t="n">
-        <v>6762573</v>
+        <v>6762554</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,10 +4904,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120487553</v>
+        <v>120487519</v>
       </c>
       <c r="B42" t="n">
-        <v>90864</v>
+        <v>79160</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4898,43 +4920,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440453</v>
+        <v>440543</v>
       </c>
       <c r="R42" t="n">
-        <v>6762571</v>
+        <v>6762378</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,10 +5006,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120487609</v>
+        <v>120487582</v>
       </c>
       <c r="B43" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5009,21 +5022,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5033,10 +5046,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440568</v>
+        <v>440609</v>
       </c>
       <c r="R43" t="n">
-        <v>6762302</v>
+        <v>6762652</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5095,7 +5108,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120487579</v>
+        <v>120487576</v>
       </c>
       <c r="B44" t="n">
         <v>78542</v>
@@ -5135,10 +5148,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440787</v>
+        <v>440924</v>
       </c>
       <c r="R44" t="n">
-        <v>6762574</v>
+        <v>6762515</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,10 +5210,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120487571</v>
+        <v>120487589</v>
       </c>
       <c r="B45" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5213,21 +5226,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5237,10 +5250,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440538</v>
+        <v>440562</v>
       </c>
       <c r="R45" t="n">
-        <v>6762461</v>
+        <v>6762505</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5299,10 +5312,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120487572</v>
+        <v>120487570</v>
       </c>
       <c r="B46" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5311,38 +5324,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440472</v>
+        <v>440493</v>
       </c>
       <c r="R46" t="n">
-        <v>6762543</v>
+        <v>6762565</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5401,10 +5423,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120487563</v>
+        <v>120487553</v>
       </c>
       <c r="B47" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5413,35 +5435,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5450,10 +5472,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440538</v>
+        <v>440453</v>
       </c>
       <c r="R47" t="n">
-        <v>6762562</v>
+        <v>6762571</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5512,10 +5534,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120487603</v>
+        <v>120487542</v>
       </c>
       <c r="B48" t="n">
-        <v>78187</v>
+        <v>91023</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5524,38 +5546,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440806</v>
+        <v>440487</v>
       </c>
       <c r="R48" t="n">
-        <v>6762547</v>
+        <v>6762566</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5614,10 +5645,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120487547</v>
+        <v>120487546</v>
       </c>
       <c r="B49" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5626,25 +5657,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5663,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>440497</v>
+        <v>440451</v>
       </c>
       <c r="R49" t="n">
-        <v>6762586</v>
+        <v>6762569</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5725,10 +5756,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120487555</v>
+        <v>120487604</v>
       </c>
       <c r="B50" t="n">
-        <v>90864</v>
+        <v>78187</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5741,43 +5772,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440492</v>
+        <v>440546</v>
       </c>
       <c r="R50" t="n">
-        <v>6762568</v>
+        <v>6762499</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5836,10 +5858,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120487589</v>
+        <v>120487568</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5848,38 +5870,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440562</v>
+        <v>440543</v>
       </c>
       <c r="R51" t="n">
-        <v>6762505</v>
+        <v>6762564</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5912,6 +5943,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2 blomstjälkar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5938,10 +5974,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120487587</v>
+        <v>120487610</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5954,21 +5990,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5978,10 +6014,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440498</v>
+        <v>440703</v>
       </c>
       <c r="R52" t="n">
-        <v>6762553</v>
+        <v>6762265</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6040,10 +6076,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120487546</v>
+        <v>120487574</v>
       </c>
       <c r="B53" t="n">
-        <v>91023</v>
+        <v>90794</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6052,47 +6088,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1209</v>
+        <v>1101</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>440451</v>
+        <v>440750</v>
       </c>
       <c r="R53" t="n">
-        <v>6762569</v>
+        <v>6762682</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6133,6 +6160,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6151,10 +6179,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120487565</v>
+        <v>120487531</v>
       </c>
       <c r="B54" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6163,47 +6191,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>440511</v>
+        <v>440460</v>
       </c>
       <c r="R54" t="n">
-        <v>6762596</v>
+        <v>6762566</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6262,10 +6281,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120487567</v>
+        <v>120487578</v>
       </c>
       <c r="B55" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6274,47 +6293,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440437</v>
+        <v>440797</v>
       </c>
       <c r="R55" t="n">
-        <v>6762574</v>
+        <v>6762562</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6373,10 +6383,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120487578</v>
+        <v>120487556</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6389,34 +6399,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440797</v>
+        <v>440495</v>
       </c>
       <c r="R56" t="n">
-        <v>6762562</v>
+        <v>6762580</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6475,10 +6494,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120487551</v>
+        <v>120487532</v>
       </c>
       <c r="B57" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6491,43 +6510,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>440487</v>
+        <v>440434</v>
       </c>
       <c r="R57" t="n">
-        <v>6762567</v>
+        <v>6762573</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6586,10 +6596,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120487526</v>
+        <v>120487569</v>
       </c>
       <c r="B58" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6598,38 +6608,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>440561</v>
+        <v>440493</v>
       </c>
       <c r="R58" t="n">
-        <v>6762628</v>
+        <v>6762600</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6688,10 +6707,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120487554</v>
+        <v>120487537</v>
       </c>
       <c r="B59" t="n">
-        <v>90864</v>
+        <v>90600</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6704,43 +6723,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>440451</v>
+        <v>440446</v>
       </c>
       <c r="R59" t="n">
-        <v>6762570</v>
+        <v>6762551</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6799,10 +6809,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120487574</v>
+        <v>120487579</v>
       </c>
       <c r="B60" t="n">
-        <v>90794</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6815,21 +6825,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1101</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6839,10 +6849,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>440750</v>
+        <v>440787</v>
       </c>
       <c r="R60" t="n">
-        <v>6762682</v>
+        <v>6762574</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6883,7 +6893,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6902,10 +6911,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120487570</v>
+        <v>120487588</v>
       </c>
       <c r="B61" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6914,47 +6923,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>440493</v>
+        <v>440541</v>
       </c>
       <c r="R61" t="n">
-        <v>6762565</v>
+        <v>6762542</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120487581</v>
+        <v>120487526</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7029,21 +7029,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440773</v>
+        <v>440561</v>
       </c>
       <c r="R62" t="n">
-        <v>6762656</v>
+        <v>6762628</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7115,10 +7115,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120487577</v>
+        <v>120487552</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7131,34 +7131,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440831</v>
+        <v>440453</v>
       </c>
       <c r="R63" t="n">
-        <v>6762542</v>
+        <v>6762573</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7217,10 +7226,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120487599</v>
+        <v>120487577</v>
       </c>
       <c r="B64" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7229,47 +7238,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440668</v>
+        <v>440831</v>
       </c>
       <c r="R64" t="n">
-        <v>6762281</v>
+        <v>6762542</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 41447-2024 artfynd.xlsx
+++ b/artfynd/A 41447-2024 artfynd.xlsx
@@ -2463,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487565</v>
+        <v>120487606</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,47 +2475,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440511</v>
+        <v>440535</v>
       </c>
       <c r="R19" t="n">
-        <v>6762596</v>
+        <v>6762367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,10 +2565,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487606</v>
+        <v>120487565</v>
       </c>
       <c r="B20" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2586,38 +2577,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440535</v>
+        <v>440511</v>
       </c>
       <c r="R20" t="n">
-        <v>6762367</v>
+        <v>6762596</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120487543</v>
+        <v>120487528</v>
       </c>
       <c r="B34" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4082,47 +4082,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>440483</v>
+        <v>440485</v>
       </c>
       <c r="R34" t="n">
-        <v>6762569</v>
+        <v>6762599</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4181,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120487528</v>
+        <v>120487543</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4193,38 +4184,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>440485</v>
+        <v>440483</v>
       </c>
       <c r="R35" t="n">
-        <v>6762599</v>
+        <v>6762569</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120487609</v>
+        <v>120487519</v>
       </c>
       <c r="B40" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4716,21 +4716,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440568</v>
+        <v>440543</v>
       </c>
       <c r="R40" t="n">
-        <v>6762302</v>
+        <v>6762378</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,10 +4802,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120487533</v>
+        <v>120487582</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4818,21 +4818,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440545</v>
+        <v>440609</v>
       </c>
       <c r="R41" t="n">
-        <v>6762554</v>
+        <v>6762652</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120487519</v>
+        <v>120487576</v>
       </c>
       <c r="B42" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>440543</v>
+        <v>440924</v>
       </c>
       <c r="R42" t="n">
-        <v>6762378</v>
+        <v>6762515</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120487582</v>
+        <v>120487589</v>
       </c>
       <c r="B43" t="n">
         <v>78542</v>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440609</v>
+        <v>440562</v>
       </c>
       <c r="R43" t="n">
-        <v>6762652</v>
+        <v>6762505</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120487576</v>
+        <v>120487570</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5120,38 +5120,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440924</v>
+        <v>440493</v>
       </c>
       <c r="R44" t="n">
-        <v>6762515</v>
+        <v>6762565</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5210,10 +5219,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120487589</v>
+        <v>120487533</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5226,21 +5235,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5250,10 +5259,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440562</v>
+        <v>440545</v>
       </c>
       <c r="R45" t="n">
-        <v>6762505</v>
+        <v>6762554</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5312,10 +5321,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120487570</v>
+        <v>120487609</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5324,47 +5333,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>440493</v>
+        <v>440568</v>
       </c>
       <c r="R46" t="n">
-        <v>6762565</v>
+        <v>6762302</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -7013,10 +7013,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120487526</v>
+        <v>120487577</v>
       </c>
       <c r="B62" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7029,21 +7029,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>440561</v>
+        <v>440831</v>
       </c>
       <c r="R62" t="n">
-        <v>6762628</v>
+        <v>6762542</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7115,10 +7115,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120487552</v>
+        <v>120487526</v>
       </c>
       <c r="B63" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7131,43 +7131,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>440453</v>
+        <v>440561</v>
       </c>
       <c r="R63" t="n">
-        <v>6762573</v>
+        <v>6762628</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7226,10 +7217,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120487577</v>
+        <v>120487552</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7242,34 +7233,43 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>440831</v>
+        <v>440453</v>
       </c>
       <c r="R64" t="n">
-        <v>6762542</v>
+        <v>6762573</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 41447-2024 artfynd.xlsx
+++ b/artfynd/A 41447-2024 artfynd.xlsx
@@ -8256,10 +8256,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120966250</v>
+        <v>120966270</v>
       </c>
       <c r="B74" t="n">
-        <v>78243</v>
+        <v>91963</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8268,25 +8268,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440671</v>
+        <v>440704</v>
       </c>
       <c r="R74" t="n">
-        <v>6762211</v>
+        <v>6762526</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8358,10 +8358,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120966256</v>
+        <v>120966250</v>
       </c>
       <c r="B75" t="n">
-        <v>56560</v>
+        <v>78243</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8370,54 +8370,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440567</v>
+        <v>440671</v>
       </c>
       <c r="R75" t="n">
-        <v>6762744</v>
+        <v>6762211</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8476,10 +8460,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120966270</v>
+        <v>120966256</v>
       </c>
       <c r="B76" t="n">
-        <v>91963</v>
+        <v>56560</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8492,34 +8476,50 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440704</v>
+        <v>440567</v>
       </c>
       <c r="R76" t="n">
-        <v>6762526</v>
+        <v>6762744</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10312,10 +10312,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120966246</v>
+        <v>120966243</v>
       </c>
       <c r="B94" t="n">
-        <v>78243</v>
+        <v>78632</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10328,21 +10328,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440480</v>
+        <v>440375</v>
       </c>
       <c r="R94" t="n">
-        <v>6762265</v>
+        <v>6762491</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10414,10 +10414,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120966237</v>
+        <v>120966246</v>
       </c>
       <c r="B95" t="n">
-        <v>90973</v>
+        <v>78243</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10430,21 +10430,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10454,10 +10454,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440448</v>
+        <v>440480</v>
       </c>
       <c r="R95" t="n">
-        <v>6762586</v>
+        <v>6762265</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10516,10 +10516,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120966243</v>
+        <v>120966237</v>
       </c>
       <c r="B96" t="n">
-        <v>78632</v>
+        <v>90973</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10532,21 +10532,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10556,10 +10556,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440375</v>
+        <v>440448</v>
       </c>
       <c r="R96" t="n">
-        <v>6762491</v>
+        <v>6762586</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10720,10 +10720,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120966238</v>
+        <v>120966247</v>
       </c>
       <c r="B98" t="n">
-        <v>90687</v>
+        <v>78243</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10736,21 +10736,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10760,10 +10760,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440448</v>
+        <v>440372</v>
       </c>
       <c r="R98" t="n">
-        <v>6762586</v>
+        <v>6762379</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10822,10 +10822,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120966252</v>
+        <v>120966238</v>
       </c>
       <c r="B99" t="n">
-        <v>79216</v>
+        <v>90687</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10838,21 +10838,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10862,10 +10862,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440501</v>
+        <v>440448</v>
       </c>
       <c r="R99" t="n">
-        <v>6762669</v>
+        <v>6762586</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10924,10 +10924,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120966247</v>
+        <v>120966252</v>
       </c>
       <c r="B100" t="n">
-        <v>78243</v>
+        <v>79216</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10940,21 +10940,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10964,10 +10964,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440372</v>
+        <v>440501</v>
       </c>
       <c r="R100" t="n">
-        <v>6762379</v>
+        <v>6762669</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>

--- a/artfynd/A 41447-2024 artfynd.xlsx
+++ b/artfynd/A 41447-2024 artfynd.xlsx
@@ -7328,10 +7328,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120966239</v>
+        <v>120966259</v>
       </c>
       <c r="B65" t="n">
-        <v>78243</v>
+        <v>78246</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7368,10 +7368,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440808</v>
+        <v>440440</v>
       </c>
       <c r="R65" t="n">
-        <v>6762456</v>
+        <v>6762356</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7430,10 +7430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120966265</v>
+        <v>120966239</v>
       </c>
       <c r="B66" t="n">
-        <v>78598</v>
+        <v>78246</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7446,21 +7446,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440545</v>
+        <v>440808</v>
       </c>
       <c r="R66" t="n">
-        <v>6762695</v>
+        <v>6762456</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7532,10 +7532,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120966266</v>
+        <v>120966262</v>
       </c>
       <c r="B67" t="n">
-        <v>8432</v>
+        <v>78635</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7544,43 +7544,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440633</v>
+        <v>440495</v>
       </c>
       <c r="R67" t="n">
-        <v>6762726</v>
+        <v>6762651</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7639,10 +7634,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120966264</v>
+        <v>120966266</v>
       </c>
       <c r="B68" t="n">
-        <v>78335</v>
+        <v>8432</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7651,38 +7646,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440557</v>
+        <v>440633</v>
       </c>
       <c r="R68" t="n">
-        <v>6762735</v>
+        <v>6762726</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7741,10 +7741,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120966275</v>
+        <v>120966258</v>
       </c>
       <c r="B69" t="n">
-        <v>91127</v>
+        <v>78601</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7753,25 +7753,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7781,10 +7781,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440482</v>
+        <v>440684</v>
       </c>
       <c r="R69" t="n">
-        <v>6762604</v>
+        <v>6762091</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7843,10 +7843,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120966249</v>
+        <v>120966256</v>
       </c>
       <c r="B70" t="n">
-        <v>78598</v>
+        <v>56563</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7855,38 +7855,54 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440671</v>
+        <v>440567</v>
       </c>
       <c r="R70" t="n">
-        <v>6762211</v>
+        <v>6762744</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7945,10 +7961,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120966278</v>
+        <v>120966243</v>
       </c>
       <c r="B71" t="n">
-        <v>78598</v>
+        <v>78635</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7961,21 +7977,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7985,10 +8001,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440799</v>
+        <v>440375</v>
       </c>
       <c r="R71" t="n">
-        <v>6762494</v>
+        <v>6762491</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8047,10 +8063,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120966248</v>
+        <v>120966269</v>
       </c>
       <c r="B72" t="n">
-        <v>5189</v>
+        <v>78246</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8059,43 +8075,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>105930</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440708</v>
+        <v>440498</v>
       </c>
       <c r="R72" t="n">
-        <v>6762633</v>
+        <v>6762240</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8154,10 +8165,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120966244</v>
+        <v>120966270</v>
       </c>
       <c r="B73" t="n">
-        <v>79216</v>
+        <v>91973</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8166,25 +8177,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8194,10 +8205,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440352</v>
+        <v>440704</v>
       </c>
       <c r="R73" t="n">
-        <v>6762430</v>
+        <v>6762526</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8256,10 +8267,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120966270</v>
+        <v>120966250</v>
       </c>
       <c r="B74" t="n">
-        <v>91963</v>
+        <v>78246</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8268,25 +8279,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8296,10 +8307,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440704</v>
+        <v>440671</v>
       </c>
       <c r="R74" t="n">
-        <v>6762526</v>
+        <v>6762211</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8358,10 +8369,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120966250</v>
+        <v>120966246</v>
       </c>
       <c r="B75" t="n">
-        <v>78243</v>
+        <v>78246</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8398,10 +8409,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440671</v>
+        <v>440480</v>
       </c>
       <c r="R75" t="n">
-        <v>6762211</v>
+        <v>6762265</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8460,10 +8471,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120966256</v>
+        <v>120966265</v>
       </c>
       <c r="B76" t="n">
-        <v>56560</v>
+        <v>78601</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8472,54 +8483,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440567</v>
+        <v>440545</v>
       </c>
       <c r="R76" t="n">
-        <v>6762744</v>
+        <v>6762695</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8578,10 +8573,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120966262</v>
+        <v>120966240</v>
       </c>
       <c r="B77" t="n">
-        <v>78632</v>
+        <v>90697</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8594,21 +8589,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8618,10 +8613,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440495</v>
+        <v>440480</v>
       </c>
       <c r="R77" t="n">
-        <v>6762651</v>
+        <v>6762601</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8680,10 +8675,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120966234</v>
+        <v>120966242</v>
       </c>
       <c r="B78" t="n">
-        <v>91127</v>
+        <v>78601</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8692,25 +8687,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8720,10 +8715,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440462</v>
+        <v>440375</v>
       </c>
       <c r="R78" t="n">
-        <v>6762578</v>
+        <v>6762491</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8782,10 +8777,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120966261</v>
+        <v>120966253</v>
       </c>
       <c r="B79" t="n">
-        <v>90973</v>
+        <v>78338</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8798,21 +8793,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8822,10 +8817,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440459</v>
+        <v>440501</v>
       </c>
       <c r="R79" t="n">
-        <v>6762577</v>
+        <v>6762669</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8884,10 +8879,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120966258</v>
+        <v>120966234</v>
       </c>
       <c r="B80" t="n">
-        <v>78598</v>
+        <v>91137</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8896,25 +8891,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8924,10 +8919,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440684</v>
+        <v>440462</v>
       </c>
       <c r="R80" t="n">
-        <v>6762091</v>
+        <v>6762578</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8986,10 +8981,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120966260</v>
+        <v>120966249</v>
       </c>
       <c r="B81" t="n">
-        <v>91127</v>
+        <v>78601</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8998,25 +8993,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9026,10 +9021,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440459</v>
+        <v>440671</v>
       </c>
       <c r="R81" t="n">
-        <v>6762577</v>
+        <v>6762211</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9088,10 +9083,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120966276</v>
+        <v>120966275</v>
       </c>
       <c r="B82" t="n">
-        <v>90973</v>
+        <v>91137</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9100,25 +9095,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9190,10 +9185,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120966255</v>
+        <v>120966273</v>
       </c>
       <c r="B83" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9206,21 +9201,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9230,10 +9225,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440452</v>
+        <v>440608</v>
       </c>
       <c r="R83" t="n">
-        <v>6762628</v>
+        <v>6762207</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9292,10 +9287,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120966240</v>
+        <v>120966264</v>
       </c>
       <c r="B84" t="n">
-        <v>90687</v>
+        <v>78338</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9308,21 +9303,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9332,10 +9327,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440480</v>
+        <v>440557</v>
       </c>
       <c r="R84" t="n">
-        <v>6762601</v>
+        <v>6762735</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9394,10 +9389,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120966273</v>
+        <v>120966261</v>
       </c>
       <c r="B85" t="n">
-        <v>78598</v>
+        <v>90983</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9410,21 +9405,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9434,10 +9429,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440608</v>
+        <v>440459</v>
       </c>
       <c r="R85" t="n">
-        <v>6762207</v>
+        <v>6762577</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9496,10 +9491,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120966242</v>
+        <v>120966274</v>
       </c>
       <c r="B86" t="n">
-        <v>78598</v>
+        <v>78337</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9512,21 +9507,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9536,10 +9531,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440375</v>
+        <v>440467</v>
       </c>
       <c r="R86" t="n">
-        <v>6762491</v>
+        <v>6762625</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9598,10 +9593,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120966259</v>
+        <v>120966251</v>
       </c>
       <c r="B87" t="n">
-        <v>78243</v>
+        <v>90623</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9614,21 +9609,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9638,10 +9633,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440440</v>
+        <v>440671</v>
       </c>
       <c r="R87" t="n">
-        <v>6762356</v>
+        <v>6762211</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9700,10 +9695,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120966253</v>
+        <v>120966244</v>
       </c>
       <c r="B88" t="n">
-        <v>78335</v>
+        <v>79219</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9716,21 +9711,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9740,10 +9735,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440501</v>
+        <v>440352</v>
       </c>
       <c r="R88" t="n">
-        <v>6762669</v>
+        <v>6762430</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9802,10 +9797,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120966277</v>
+        <v>120966237</v>
       </c>
       <c r="B89" t="n">
-        <v>90687</v>
+        <v>90983</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9818,21 +9813,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9842,10 +9837,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440482</v>
+        <v>440448</v>
       </c>
       <c r="R89" t="n">
-        <v>6762604</v>
+        <v>6762586</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9904,10 +9899,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120966272</v>
+        <v>120966277</v>
       </c>
       <c r="B90" t="n">
-        <v>78334</v>
+        <v>90697</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9920,21 +9915,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9944,10 +9939,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440473</v>
+        <v>440482</v>
       </c>
       <c r="R90" t="n">
-        <v>6762625</v>
+        <v>6762604</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10006,10 +10001,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120966269</v>
+        <v>120966236</v>
       </c>
       <c r="B91" t="n">
-        <v>78243</v>
+        <v>79219</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10022,21 +10017,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10046,10 +10041,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440498</v>
+        <v>440715</v>
       </c>
       <c r="R91" t="n">
-        <v>6762240</v>
+        <v>6762301</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10108,10 +10103,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120966236</v>
+        <v>120966272</v>
       </c>
       <c r="B92" t="n">
-        <v>79216</v>
+        <v>78337</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10124,21 +10119,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10148,10 +10143,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440715</v>
+        <v>440473</v>
       </c>
       <c r="R92" t="n">
-        <v>6762301</v>
+        <v>6762625</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10210,10 +10205,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120966251</v>
+        <v>120966247</v>
       </c>
       <c r="B93" t="n">
-        <v>90613</v>
+        <v>78246</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10226,21 +10221,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10250,10 +10245,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440671</v>
+        <v>440372</v>
       </c>
       <c r="R93" t="n">
-        <v>6762211</v>
+        <v>6762379</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10312,10 +10307,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120966243</v>
+        <v>120966278</v>
       </c>
       <c r="B94" t="n">
-        <v>78632</v>
+        <v>78601</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10328,21 +10323,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10352,10 +10347,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440375</v>
+        <v>440799</v>
       </c>
       <c r="R94" t="n">
-        <v>6762491</v>
+        <v>6762494</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10414,10 +10409,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120966246</v>
+        <v>120966271</v>
       </c>
       <c r="B95" t="n">
-        <v>78243</v>
+        <v>56563</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10426,38 +10421,54 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440480</v>
+        <v>440380</v>
       </c>
       <c r="R95" t="n">
-        <v>6762265</v>
+        <v>6762477</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10516,10 +10527,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120966237</v>
+        <v>120966241</v>
       </c>
       <c r="B96" t="n">
-        <v>90973</v>
+        <v>78635</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10532,21 +10543,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10556,10 +10567,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440448</v>
+        <v>440376</v>
       </c>
       <c r="R96" t="n">
-        <v>6762586</v>
+        <v>6762458</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10618,10 +10629,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120966268</v>
+        <v>120966255</v>
       </c>
       <c r="B97" t="n">
-        <v>92160</v>
+        <v>74708</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10634,21 +10645,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2079</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10658,10 +10669,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440498</v>
+        <v>440452</v>
       </c>
       <c r="R97" t="n">
-        <v>6762240</v>
+        <v>6762628</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10720,10 +10731,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120966247</v>
+        <v>120966252</v>
       </c>
       <c r="B98" t="n">
-        <v>78243</v>
+        <v>79219</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10736,21 +10747,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10760,10 +10771,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440372</v>
+        <v>440501</v>
       </c>
       <c r="R98" t="n">
-        <v>6762379</v>
+        <v>6762669</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10822,10 +10833,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120966238</v>
+        <v>120966276</v>
       </c>
       <c r="B99" t="n">
-        <v>90687</v>
+        <v>90983</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10838,21 +10849,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10862,10 +10873,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440448</v>
+        <v>440482</v>
       </c>
       <c r="R99" t="n">
-        <v>6762586</v>
+        <v>6762604</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10924,10 +10935,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120966252</v>
+        <v>120966238</v>
       </c>
       <c r="B100" t="n">
-        <v>79216</v>
+        <v>90697</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10940,21 +10951,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10964,10 +10975,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440501</v>
+        <v>440448</v>
       </c>
       <c r="R100" t="n">
-        <v>6762669</v>
+        <v>6762586</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11026,10 +11037,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120966274</v>
+        <v>120966268</v>
       </c>
       <c r="B101" t="n">
-        <v>78334</v>
+        <v>92170</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11042,21 +11053,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11066,10 +11077,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440467</v>
+        <v>440498</v>
       </c>
       <c r="R101" t="n">
-        <v>6762625</v>
+        <v>6762240</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11128,10 +11139,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120966271</v>
+        <v>120966248</v>
       </c>
       <c r="B102" t="n">
-        <v>56560</v>
+        <v>5189</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11144,50 +11155,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440380</v>
+        <v>440708</v>
       </c>
       <c r="R102" t="n">
-        <v>6762477</v>
+        <v>6762633</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11246,10 +11246,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120966241</v>
+        <v>120966260</v>
       </c>
       <c r="B103" t="n">
-        <v>78632</v>
+        <v>91137</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11258,25 +11258,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11286,10 +11286,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440376</v>
+        <v>440459</v>
       </c>
       <c r="R103" t="n">
-        <v>6762458</v>
+        <v>6762577</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>

--- a/artfynd/A 41447-2024 artfynd.xlsx
+++ b/artfynd/A 41447-2024 artfynd.xlsx
@@ -7328,10 +7328,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120966259</v>
+        <v>120966244</v>
       </c>
       <c r="B65" t="n">
-        <v>78246</v>
+        <v>79219</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7344,21 +7344,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7368,10 +7368,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440440</v>
+        <v>440352</v>
       </c>
       <c r="R65" t="n">
-        <v>6762356</v>
+        <v>6762430</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7430,7 +7430,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120966239</v>
+        <v>120966250</v>
       </c>
       <c r="B66" t="n">
         <v>78246</v>
@@ -7470,10 +7470,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440808</v>
+        <v>440671</v>
       </c>
       <c r="R66" t="n">
-        <v>6762456</v>
+        <v>6762211</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7532,10 +7532,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120966262</v>
+        <v>120966237</v>
       </c>
       <c r="B67" t="n">
-        <v>78635</v>
+        <v>90983</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7548,21 +7548,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7572,10 +7572,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440495</v>
+        <v>440448</v>
       </c>
       <c r="R67" t="n">
-        <v>6762651</v>
+        <v>6762586</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120966266</v>
+        <v>120966255</v>
       </c>
       <c r="B68" t="n">
-        <v>8432</v>
+        <v>74708</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7646,43 +7646,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440633</v>
+        <v>440452</v>
       </c>
       <c r="R68" t="n">
-        <v>6762726</v>
+        <v>6762628</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7741,7 +7736,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120966258</v>
+        <v>120966273</v>
       </c>
       <c r="B69" t="n">
         <v>78601</v>
@@ -7781,10 +7776,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440684</v>
+        <v>440608</v>
       </c>
       <c r="R69" t="n">
-        <v>6762091</v>
+        <v>6762207</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7843,10 +7838,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120966256</v>
+        <v>120966241</v>
       </c>
       <c r="B70" t="n">
-        <v>56563</v>
+        <v>78635</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7855,54 +7850,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440567</v>
+        <v>440376</v>
       </c>
       <c r="R70" t="n">
-        <v>6762744</v>
+        <v>6762458</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7961,10 +7940,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120966243</v>
+        <v>120966239</v>
       </c>
       <c r="B71" t="n">
-        <v>78635</v>
+        <v>78246</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7977,21 +7956,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8001,10 +7980,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440375</v>
+        <v>440808</v>
       </c>
       <c r="R71" t="n">
-        <v>6762491</v>
+        <v>6762456</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8063,10 +8042,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120966269</v>
+        <v>120966261</v>
       </c>
       <c r="B72" t="n">
-        <v>78246</v>
+        <v>90983</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8079,21 +8058,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8103,10 +8082,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440498</v>
+        <v>440459</v>
       </c>
       <c r="R72" t="n">
-        <v>6762240</v>
+        <v>6762577</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8165,10 +8144,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120966270</v>
+        <v>120966272</v>
       </c>
       <c r="B73" t="n">
-        <v>91973</v>
+        <v>78337</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8177,25 +8156,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8205,10 +8184,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440704</v>
+        <v>440473</v>
       </c>
       <c r="R73" t="n">
-        <v>6762526</v>
+        <v>6762625</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8267,10 +8246,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120966250</v>
+        <v>120966277</v>
       </c>
       <c r="B74" t="n">
-        <v>78246</v>
+        <v>90697</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8283,21 +8262,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8307,10 +8286,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440671</v>
+        <v>440482</v>
       </c>
       <c r="R74" t="n">
-        <v>6762211</v>
+        <v>6762604</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8369,10 +8348,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120966246</v>
+        <v>120966274</v>
       </c>
       <c r="B75" t="n">
-        <v>78246</v>
+        <v>78337</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8385,21 +8364,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8409,10 +8388,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440480</v>
+        <v>440467</v>
       </c>
       <c r="R75" t="n">
-        <v>6762265</v>
+        <v>6762625</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8471,7 +8450,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120966265</v>
+        <v>120966249</v>
       </c>
       <c r="B76" t="n">
         <v>78601</v>
@@ -8511,10 +8490,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440545</v>
+        <v>440671</v>
       </c>
       <c r="R76" t="n">
-        <v>6762695</v>
+        <v>6762211</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8573,10 +8552,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120966240</v>
+        <v>120966265</v>
       </c>
       <c r="B77" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8589,21 +8568,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8613,10 +8592,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440480</v>
+        <v>440545</v>
       </c>
       <c r="R77" t="n">
-        <v>6762601</v>
+        <v>6762695</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8675,10 +8654,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120966242</v>
+        <v>120966234</v>
       </c>
       <c r="B78" t="n">
-        <v>78601</v>
+        <v>91137</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8687,25 +8666,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8715,10 +8694,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440375</v>
+        <v>440462</v>
       </c>
       <c r="R78" t="n">
-        <v>6762491</v>
+        <v>6762578</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8777,10 +8756,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120966253</v>
+        <v>120966278</v>
       </c>
       <c r="B79" t="n">
-        <v>78338</v>
+        <v>78601</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8793,21 +8772,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8817,10 +8796,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440501</v>
+        <v>440799</v>
       </c>
       <c r="R79" t="n">
-        <v>6762669</v>
+        <v>6762494</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8879,10 +8858,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120966234</v>
+        <v>120966258</v>
       </c>
       <c r="B80" t="n">
-        <v>91137</v>
+        <v>78601</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8891,25 +8870,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8919,10 +8898,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440462</v>
+        <v>440684</v>
       </c>
       <c r="R80" t="n">
-        <v>6762578</v>
+        <v>6762091</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8981,10 +8960,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120966249</v>
+        <v>120966236</v>
       </c>
       <c r="B81" t="n">
-        <v>78601</v>
+        <v>79219</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8997,21 +8976,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9021,10 +9000,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440671</v>
+        <v>440715</v>
       </c>
       <c r="R81" t="n">
-        <v>6762211</v>
+        <v>6762301</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9083,10 +9062,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120966275</v>
+        <v>120966259</v>
       </c>
       <c r="B82" t="n">
-        <v>91137</v>
+        <v>78246</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9095,25 +9074,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1209</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9123,10 +9102,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440482</v>
+        <v>440440</v>
       </c>
       <c r="R82" t="n">
-        <v>6762604</v>
+        <v>6762356</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9185,10 +9164,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120966273</v>
+        <v>120966240</v>
       </c>
       <c r="B83" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9201,21 +9180,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9225,10 +9204,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440608</v>
+        <v>440480</v>
       </c>
       <c r="R83" t="n">
-        <v>6762207</v>
+        <v>6762601</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9287,10 +9266,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120966264</v>
+        <v>120966271</v>
       </c>
       <c r="B84" t="n">
-        <v>78338</v>
+        <v>56563</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9299,38 +9278,54 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440557</v>
+        <v>440380</v>
       </c>
       <c r="R84" t="n">
-        <v>6762735</v>
+        <v>6762477</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9389,10 +9384,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120966261</v>
+        <v>120966243</v>
       </c>
       <c r="B85" t="n">
-        <v>90983</v>
+        <v>78635</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9405,21 +9400,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9429,10 +9424,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440459</v>
+        <v>440375</v>
       </c>
       <c r="R85" t="n">
-        <v>6762577</v>
+        <v>6762491</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9491,10 +9486,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120966274</v>
+        <v>120966276</v>
       </c>
       <c r="B86" t="n">
-        <v>78337</v>
+        <v>90983</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9507,21 +9502,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9531,10 +9526,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440467</v>
+        <v>440482</v>
       </c>
       <c r="R86" t="n">
-        <v>6762625</v>
+        <v>6762604</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9593,10 +9588,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120966251</v>
+        <v>120966264</v>
       </c>
       <c r="B87" t="n">
-        <v>90623</v>
+        <v>78338</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9609,21 +9604,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9633,10 +9628,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440671</v>
+        <v>440557</v>
       </c>
       <c r="R87" t="n">
-        <v>6762211</v>
+        <v>6762735</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9695,10 +9690,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120966244</v>
+        <v>120966238</v>
       </c>
       <c r="B88" t="n">
-        <v>79219</v>
+        <v>90697</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9711,21 +9706,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9735,10 +9730,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440352</v>
+        <v>440448</v>
       </c>
       <c r="R88" t="n">
-        <v>6762430</v>
+        <v>6762586</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9797,10 +9792,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120966237</v>
+        <v>120966256</v>
       </c>
       <c r="B89" t="n">
-        <v>90983</v>
+        <v>56563</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9809,38 +9804,54 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440448</v>
+        <v>440567</v>
       </c>
       <c r="R89" t="n">
-        <v>6762586</v>
+        <v>6762744</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9899,10 +9910,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120966277</v>
+        <v>120966266</v>
       </c>
       <c r="B90" t="n">
-        <v>90697</v>
+        <v>8432</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9911,38 +9922,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440482</v>
+        <v>440633</v>
       </c>
       <c r="R90" t="n">
-        <v>6762604</v>
+        <v>6762726</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10001,10 +10017,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120966236</v>
+        <v>120966253</v>
       </c>
       <c r="B91" t="n">
-        <v>79219</v>
+        <v>78338</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10017,21 +10033,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10041,10 +10057,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440715</v>
+        <v>440501</v>
       </c>
       <c r="R91" t="n">
-        <v>6762301</v>
+        <v>6762669</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10103,10 +10119,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120966272</v>
+        <v>120966242</v>
       </c>
       <c r="B92" t="n">
-        <v>78337</v>
+        <v>78601</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10119,21 +10135,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10143,10 +10159,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440473</v>
+        <v>440375</v>
       </c>
       <c r="R92" t="n">
-        <v>6762625</v>
+        <v>6762491</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10205,7 +10221,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120966247</v>
+        <v>120966269</v>
       </c>
       <c r="B93" t="n">
         <v>78246</v>
@@ -10245,10 +10261,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440372</v>
+        <v>440498</v>
       </c>
       <c r="R93" t="n">
-        <v>6762379</v>
+        <v>6762240</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10307,10 +10323,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120966278</v>
+        <v>120966247</v>
       </c>
       <c r="B94" t="n">
-        <v>78601</v>
+        <v>78246</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10323,21 +10339,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10347,10 +10363,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440799</v>
+        <v>440372</v>
       </c>
       <c r="R94" t="n">
-        <v>6762494</v>
+        <v>6762379</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10409,10 +10425,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120966271</v>
+        <v>120966275</v>
       </c>
       <c r="B95" t="n">
-        <v>56563</v>
+        <v>91137</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10421,54 +10437,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440380</v>
+        <v>440482</v>
       </c>
       <c r="R95" t="n">
-        <v>6762477</v>
+        <v>6762604</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10527,10 +10527,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120966241</v>
+        <v>120966251</v>
       </c>
       <c r="B96" t="n">
-        <v>78635</v>
+        <v>90623</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10543,21 +10543,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>185</v>
+        <v>3242</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10567,10 +10567,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440376</v>
+        <v>440671</v>
       </c>
       <c r="R96" t="n">
-        <v>6762458</v>
+        <v>6762211</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10629,10 +10629,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120966255</v>
+        <v>120966252</v>
       </c>
       <c r="B97" t="n">
-        <v>74708</v>
+        <v>79219</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10645,21 +10645,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10669,10 +10669,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440452</v>
+        <v>440501</v>
       </c>
       <c r="R97" t="n">
-        <v>6762628</v>
+        <v>6762669</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10731,10 +10731,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120966252</v>
+        <v>120966260</v>
       </c>
       <c r="B98" t="n">
-        <v>79219</v>
+        <v>91137</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10743,25 +10743,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10771,10 +10771,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440501</v>
+        <v>440459</v>
       </c>
       <c r="R98" t="n">
-        <v>6762669</v>
+        <v>6762577</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10833,10 +10833,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120966276</v>
+        <v>120966246</v>
       </c>
       <c r="B99" t="n">
-        <v>90983</v>
+        <v>78246</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10849,21 +10849,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10873,10 +10873,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440482</v>
+        <v>440480</v>
       </c>
       <c r="R99" t="n">
-        <v>6762604</v>
+        <v>6762265</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10935,10 +10935,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120966238</v>
+        <v>120966262</v>
       </c>
       <c r="B100" t="n">
-        <v>90697</v>
+        <v>78635</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10951,21 +10951,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10975,10 +10975,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440448</v>
+        <v>440495</v>
       </c>
       <c r="R100" t="n">
-        <v>6762586</v>
+        <v>6762651</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11037,10 +11037,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120966268</v>
+        <v>120966270</v>
       </c>
       <c r="B101" t="n">
-        <v>92170</v>
+        <v>91973</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11049,25 +11049,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11077,10 +11077,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440498</v>
+        <v>440704</v>
       </c>
       <c r="R101" t="n">
-        <v>6762240</v>
+        <v>6762526</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11139,10 +11139,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120966248</v>
+        <v>120966268</v>
       </c>
       <c r="B102" t="n">
-        <v>5189</v>
+        <v>92170</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11151,43 +11151,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>105930</v>
+        <v>2079</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440708</v>
+        <v>440498</v>
       </c>
       <c r="R102" t="n">
-        <v>6762633</v>
+        <v>6762240</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11246,10 +11241,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120966260</v>
+        <v>120966248</v>
       </c>
       <c r="B103" t="n">
-        <v>91137</v>
+        <v>5189</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11258,38 +11253,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
+        <v>105930</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440459</v>
+        <v>440708</v>
       </c>
       <c r="R103" t="n">
-        <v>6762577</v>
+        <v>6762633</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>

--- a/artfynd/A 41447-2024 artfynd.xlsx
+++ b/artfynd/A 41447-2024 artfynd.xlsx
@@ -9690,10 +9690,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120966238</v>
+        <v>120966256</v>
       </c>
       <c r="B88" t="n">
-        <v>90697</v>
+        <v>56563</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9702,38 +9702,54 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440448</v>
+        <v>440567</v>
       </c>
       <c r="R88" t="n">
-        <v>6762586</v>
+        <v>6762744</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9792,10 +9808,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120966256</v>
+        <v>120966266</v>
       </c>
       <c r="B89" t="n">
-        <v>56563</v>
+        <v>8432</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9808,50 +9824,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440567</v>
+        <v>440633</v>
       </c>
       <c r="R89" t="n">
-        <v>6762744</v>
+        <v>6762726</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9910,10 +9915,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120966266</v>
+        <v>120966238</v>
       </c>
       <c r="B90" t="n">
-        <v>8432</v>
+        <v>90697</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9922,43 +9927,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440633</v>
+        <v>440448</v>
       </c>
       <c r="R90" t="n">
-        <v>6762726</v>
+        <v>6762586</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10017,10 +10017,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120966253</v>
+        <v>120966242</v>
       </c>
       <c r="B91" t="n">
-        <v>78338</v>
+        <v>78601</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10033,21 +10033,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10057,10 +10057,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440501</v>
+        <v>440375</v>
       </c>
       <c r="R91" t="n">
-        <v>6762669</v>
+        <v>6762491</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10119,10 +10119,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120966242</v>
+        <v>120966269</v>
       </c>
       <c r="B92" t="n">
-        <v>78601</v>
+        <v>78246</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10135,21 +10135,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440375</v>
+        <v>440498</v>
       </c>
       <c r="R92" t="n">
-        <v>6762491</v>
+        <v>6762240</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10221,7 +10221,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120966269</v>
+        <v>120966247</v>
       </c>
       <c r="B93" t="n">
         <v>78246</v>
@@ -10261,10 +10261,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440498</v>
+        <v>440372</v>
       </c>
       <c r="R93" t="n">
-        <v>6762240</v>
+        <v>6762379</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10323,10 +10323,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120966247</v>
+        <v>120966275</v>
       </c>
       <c r="B94" t="n">
-        <v>78246</v>
+        <v>91137</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10335,25 +10335,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>1209</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10363,10 +10363,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440372</v>
+        <v>440482</v>
       </c>
       <c r="R94" t="n">
-        <v>6762379</v>
+        <v>6762604</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120966275</v>
+        <v>120966253</v>
       </c>
       <c r="B95" t="n">
-        <v>91137</v>
+        <v>78338</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10437,25 +10437,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1209</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440482</v>
+        <v>440501</v>
       </c>
       <c r="R95" t="n">
-        <v>6762604</v>
+        <v>6762669</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11037,10 +11037,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120966270</v>
+        <v>120966248</v>
       </c>
       <c r="B101" t="n">
-        <v>91973</v>
+        <v>5189</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11053,34 +11053,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440704</v>
+        <v>440708</v>
       </c>
       <c r="R101" t="n">
-        <v>6762526</v>
+        <v>6762633</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11139,10 +11144,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120966268</v>
+        <v>120966270</v>
       </c>
       <c r="B102" t="n">
-        <v>92170</v>
+        <v>91973</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11151,25 +11156,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11179,10 +11184,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440498</v>
+        <v>440704</v>
       </c>
       <c r="R102" t="n">
-        <v>6762240</v>
+        <v>6762526</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11241,10 +11246,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120966248</v>
+        <v>120966268</v>
       </c>
       <c r="B103" t="n">
-        <v>5189</v>
+        <v>92170</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11253,43 +11258,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>105930</v>
+        <v>2079</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440708</v>
+        <v>440498</v>
       </c>
       <c r="R103" t="n">
-        <v>6762633</v>
+        <v>6762240</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>

--- a/artfynd/A 41447-2024 artfynd.xlsx
+++ b/artfynd/A 41447-2024 artfynd.xlsx
@@ -7328,10 +7328,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120966244</v>
+        <v>120966273</v>
       </c>
       <c r="B65" t="n">
-        <v>79219</v>
+        <v>78604</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7344,21 +7344,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7368,10 +7368,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>440352</v>
+        <v>440608</v>
       </c>
       <c r="R65" t="n">
-        <v>6762430</v>
+        <v>6762207</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7430,10 +7430,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120966250</v>
+        <v>120966256</v>
       </c>
       <c r="B66" t="n">
-        <v>78246</v>
+        <v>56563</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7442,38 +7442,54 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>440671</v>
+        <v>440567</v>
       </c>
       <c r="R66" t="n">
-        <v>6762211</v>
+        <v>6762744</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7532,10 +7548,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120966237</v>
+        <v>120966253</v>
       </c>
       <c r="B67" t="n">
-        <v>90983</v>
+        <v>78341</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7548,21 +7564,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7572,10 +7588,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>440448</v>
+        <v>440501</v>
       </c>
       <c r="R67" t="n">
-        <v>6762586</v>
+        <v>6762669</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7634,10 +7650,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120966255</v>
+        <v>120966250</v>
       </c>
       <c r="B68" t="n">
-        <v>74708</v>
+        <v>78249</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7650,21 +7666,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7674,10 +7690,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>440452</v>
+        <v>440671</v>
       </c>
       <c r="R68" t="n">
-        <v>6762628</v>
+        <v>6762211</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7736,10 +7752,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120966273</v>
+        <v>120966260</v>
       </c>
       <c r="B69" t="n">
-        <v>78601</v>
+        <v>91149</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7748,25 +7764,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7776,10 +7792,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>440608</v>
+        <v>440459</v>
       </c>
       <c r="R69" t="n">
-        <v>6762207</v>
+        <v>6762577</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7838,10 +7854,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120966241</v>
+        <v>120966249</v>
       </c>
       <c r="B70" t="n">
-        <v>78635</v>
+        <v>78604</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7854,21 +7870,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7878,10 +7894,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>440376</v>
+        <v>440671</v>
       </c>
       <c r="R70" t="n">
-        <v>6762458</v>
+        <v>6762211</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7940,10 +7956,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120966239</v>
+        <v>120966276</v>
       </c>
       <c r="B71" t="n">
-        <v>78246</v>
+        <v>90995</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7956,21 +7972,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7980,10 +7996,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>440808</v>
+        <v>440482</v>
       </c>
       <c r="R71" t="n">
-        <v>6762456</v>
+        <v>6762604</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8042,10 +8058,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120966261</v>
+        <v>120966239</v>
       </c>
       <c r="B72" t="n">
-        <v>90983</v>
+        <v>78249</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8058,21 +8074,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8082,10 +8098,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>440459</v>
+        <v>440808</v>
       </c>
       <c r="R72" t="n">
-        <v>6762577</v>
+        <v>6762456</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8144,10 +8160,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120966272</v>
+        <v>120966275</v>
       </c>
       <c r="B73" t="n">
-        <v>78337</v>
+        <v>91149</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8156,25 +8172,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8184,10 +8200,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>440473</v>
+        <v>440482</v>
       </c>
       <c r="R73" t="n">
-        <v>6762625</v>
+        <v>6762604</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8246,10 +8262,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120966277</v>
+        <v>120966278</v>
       </c>
       <c r="B74" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8262,21 +8278,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8286,10 +8302,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>440482</v>
+        <v>440799</v>
       </c>
       <c r="R74" t="n">
-        <v>6762604</v>
+        <v>6762494</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8348,10 +8364,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120966274</v>
+        <v>120966236</v>
       </c>
       <c r="B75" t="n">
-        <v>78337</v>
+        <v>79222</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8364,21 +8380,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8388,10 +8404,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>440467</v>
+        <v>440715</v>
       </c>
       <c r="R75" t="n">
-        <v>6762625</v>
+        <v>6762301</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8450,10 +8466,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120966249</v>
+        <v>120966243</v>
       </c>
       <c r="B76" t="n">
-        <v>78601</v>
+        <v>78638</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8466,21 +8482,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8490,10 +8506,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>440671</v>
+        <v>440375</v>
       </c>
       <c r="R76" t="n">
-        <v>6762211</v>
+        <v>6762491</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8552,10 +8568,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120966265</v>
+        <v>120966242</v>
       </c>
       <c r="B77" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8592,10 +8608,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>440545</v>
+        <v>440375</v>
       </c>
       <c r="R77" t="n">
-        <v>6762695</v>
+        <v>6762491</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8654,10 +8670,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120966234</v>
+        <v>120966274</v>
       </c>
       <c r="B78" t="n">
-        <v>91137</v>
+        <v>78340</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8666,25 +8682,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8694,10 +8710,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>440462</v>
+        <v>440467</v>
       </c>
       <c r="R78" t="n">
-        <v>6762578</v>
+        <v>6762625</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8756,10 +8772,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120966278</v>
+        <v>120966246</v>
       </c>
       <c r="B79" t="n">
-        <v>78601</v>
+        <v>78249</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8772,21 +8788,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8796,10 +8812,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>440799</v>
+        <v>440480</v>
       </c>
       <c r="R79" t="n">
-        <v>6762494</v>
+        <v>6762265</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,10 +8874,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120966258</v>
+        <v>120966244</v>
       </c>
       <c r="B80" t="n">
-        <v>78601</v>
+        <v>79222</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8874,21 +8890,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8898,10 +8914,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>440684</v>
+        <v>440352</v>
       </c>
       <c r="R80" t="n">
-        <v>6762091</v>
+        <v>6762430</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8960,10 +8976,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120966236</v>
+        <v>120966258</v>
       </c>
       <c r="B81" t="n">
-        <v>79219</v>
+        <v>78604</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8976,21 +8992,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9000,10 +9016,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>440715</v>
+        <v>440684</v>
       </c>
       <c r="R81" t="n">
-        <v>6762301</v>
+        <v>6762091</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9062,10 +9078,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120966259</v>
+        <v>120966272</v>
       </c>
       <c r="B82" t="n">
-        <v>78246</v>
+        <v>78340</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9078,21 +9094,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9102,10 +9118,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>440440</v>
+        <v>440473</v>
       </c>
       <c r="R82" t="n">
-        <v>6762356</v>
+        <v>6762625</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9164,10 +9180,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120966240</v>
+        <v>120966234</v>
       </c>
       <c r="B83" t="n">
-        <v>90697</v>
+        <v>91149</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9176,25 +9192,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9204,10 +9220,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>440480</v>
+        <v>440462</v>
       </c>
       <c r="R83" t="n">
-        <v>6762601</v>
+        <v>6762578</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9266,10 +9282,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120966271</v>
+        <v>120966268</v>
       </c>
       <c r="B84" t="n">
-        <v>56563</v>
+        <v>92182</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9278,54 +9294,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>440380</v>
+        <v>440498</v>
       </c>
       <c r="R84" t="n">
-        <v>6762477</v>
+        <v>6762240</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9384,10 +9384,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120966243</v>
+        <v>120966247</v>
       </c>
       <c r="B85" t="n">
-        <v>78635</v>
+        <v>78249</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9400,21 +9400,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9424,10 +9424,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>440375</v>
+        <v>440372</v>
       </c>
       <c r="R85" t="n">
-        <v>6762491</v>
+        <v>6762379</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9486,10 +9486,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120966276</v>
+        <v>120966241</v>
       </c>
       <c r="B86" t="n">
-        <v>90983</v>
+        <v>78638</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9502,21 +9502,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>440482</v>
+        <v>440376</v>
       </c>
       <c r="R86" t="n">
-        <v>6762604</v>
+        <v>6762458</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9588,10 +9588,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120966264</v>
+        <v>120966238</v>
       </c>
       <c r="B87" t="n">
-        <v>78338</v>
+        <v>90709</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9604,21 +9604,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>440557</v>
+        <v>440448</v>
       </c>
       <c r="R87" t="n">
-        <v>6762735</v>
+        <v>6762586</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9690,10 +9690,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120966256</v>
+        <v>120966269</v>
       </c>
       <c r="B88" t="n">
-        <v>56563</v>
+        <v>78249</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9702,54 +9702,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>440567</v>
+        <v>440498</v>
       </c>
       <c r="R88" t="n">
-        <v>6762744</v>
+        <v>6762240</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9808,10 +9792,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120966266</v>
+        <v>120966255</v>
       </c>
       <c r="B89" t="n">
-        <v>8432</v>
+        <v>74710</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9820,43 +9804,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>440633</v>
+        <v>440452</v>
       </c>
       <c r="R89" t="n">
-        <v>6762726</v>
+        <v>6762628</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9915,10 +9894,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120966238</v>
+        <v>120966259</v>
       </c>
       <c r="B90" t="n">
-        <v>90697</v>
+        <v>78249</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9931,21 +9910,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9955,10 +9934,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>440448</v>
+        <v>440440</v>
       </c>
       <c r="R90" t="n">
-        <v>6762586</v>
+        <v>6762356</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10017,10 +9996,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120966242</v>
+        <v>120966237</v>
       </c>
       <c r="B91" t="n">
-        <v>78601</v>
+        <v>90995</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10033,21 +10012,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10057,10 +10036,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>440375</v>
+        <v>440448</v>
       </c>
       <c r="R91" t="n">
-        <v>6762491</v>
+        <v>6762586</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10119,10 +10098,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120966269</v>
+        <v>120966277</v>
       </c>
       <c r="B92" t="n">
-        <v>78246</v>
+        <v>90709</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10135,21 +10114,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10159,10 +10138,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>440498</v>
+        <v>440482</v>
       </c>
       <c r="R92" t="n">
-        <v>6762240</v>
+        <v>6762604</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10221,10 +10200,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120966247</v>
+        <v>120966265</v>
       </c>
       <c r="B93" t="n">
-        <v>78246</v>
+        <v>78604</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10237,21 +10216,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10261,10 +10240,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>440372</v>
+        <v>440545</v>
       </c>
       <c r="R93" t="n">
-        <v>6762379</v>
+        <v>6762695</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10323,10 +10302,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120966275</v>
+        <v>120966266</v>
       </c>
       <c r="B94" t="n">
-        <v>91137</v>
+        <v>8432</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10335,38 +10314,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>440482</v>
+        <v>440633</v>
       </c>
       <c r="R94" t="n">
-        <v>6762604</v>
+        <v>6762726</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10425,10 +10409,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120966253</v>
+        <v>120966264</v>
       </c>
       <c r="B95" t="n">
-        <v>78338</v>
+        <v>78341</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10465,10 +10449,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>440501</v>
+        <v>440557</v>
       </c>
       <c r="R95" t="n">
-        <v>6762669</v>
+        <v>6762735</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10527,10 +10511,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120966251</v>
+        <v>120966261</v>
       </c>
       <c r="B96" t="n">
-        <v>90623</v>
+        <v>90995</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10543,21 +10527,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3242</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10567,10 +10551,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>440671</v>
+        <v>440459</v>
       </c>
       <c r="R96" t="n">
-        <v>6762211</v>
+        <v>6762577</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10629,10 +10613,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120966252</v>
+        <v>120966248</v>
       </c>
       <c r="B97" t="n">
-        <v>79219</v>
+        <v>5189</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10641,38 +10625,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>440501</v>
+        <v>440708</v>
       </c>
       <c r="R97" t="n">
-        <v>6762669</v>
+        <v>6762633</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10731,10 +10720,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120966260</v>
+        <v>120966251</v>
       </c>
       <c r="B98" t="n">
-        <v>91137</v>
+        <v>90635</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10743,25 +10732,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1209</v>
+        <v>3242</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10771,10 +10760,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>440459</v>
+        <v>440671</v>
       </c>
       <c r="R98" t="n">
-        <v>6762577</v>
+        <v>6762211</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10833,10 +10822,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120966246</v>
+        <v>120966270</v>
       </c>
       <c r="B99" t="n">
-        <v>78246</v>
+        <v>91985</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10845,25 +10834,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10873,10 +10862,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>440480</v>
+        <v>440704</v>
       </c>
       <c r="R99" t="n">
-        <v>6762265</v>
+        <v>6762526</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10935,10 +10924,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120966262</v>
+        <v>120966252</v>
       </c>
       <c r="B100" t="n">
-        <v>78635</v>
+        <v>79222</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10951,21 +10940,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10975,10 +10964,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>440495</v>
+        <v>440501</v>
       </c>
       <c r="R100" t="n">
-        <v>6762651</v>
+        <v>6762669</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11037,10 +11026,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120966248</v>
+        <v>120966240</v>
       </c>
       <c r="B101" t="n">
-        <v>5189</v>
+        <v>90709</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11049,43 +11038,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>440708</v>
+        <v>440480</v>
       </c>
       <c r="R101" t="n">
-        <v>6762633</v>
+        <v>6762601</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11144,10 +11128,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120966270</v>
+        <v>120966262</v>
       </c>
       <c r="B102" t="n">
-        <v>91973</v>
+        <v>78638</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11156,25 +11140,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11184,10 +11168,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>440704</v>
+        <v>440495</v>
       </c>
       <c r="R102" t="n">
-        <v>6762526</v>
+        <v>6762651</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11246,10 +11230,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120966268</v>
+        <v>120966271</v>
       </c>
       <c r="B103" t="n">
-        <v>92170</v>
+        <v>56563</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11258,38 +11242,54 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Dovsjövasseln, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>440498</v>
+        <v>440380</v>
       </c>
       <c r="R103" t="n">
-        <v>6762240</v>
+        <v>6762477</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
